--- a/full_bs.xlsx
+++ b/full_bs.xlsx
@@ -152,13 +152,13 @@
     <t xml:space="preserve">PR3</t>
   </si>
   <si>
+    <t xml:space="preserve">h3.1b</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CR3</t>
+  </si>
+  <si>
     <t xml:space="preserve">h3.2b</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CR3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">h3.1b</t>
   </si>
   <si>
     <t xml:space="preserve">ParCollege</t>
@@ -548,22 +548,22 @@
         <v>13</v>
       </c>
       <c r="E2" t="n">
-        <v>0.252188450008796</v>
+        <v>0.220084437183621</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0892283376144507</v>
+        <v>0.0781570404893205</v>
       </c>
       <c r="G2" t="n">
-        <v>2.82632689066207</v>
+        <v>2.815925933297</v>
       </c>
       <c r="H2" t="n">
-        <v>0.00470851862926812</v>
+        <v>0.00486368781346141</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0773041218840919</v>
+        <v>0.0668994526863142</v>
       </c>
       <c r="J2" t="n">
-        <v>0.4270727781335</v>
+        <v>0.373269421680928</v>
       </c>
     </row>
     <row r="3">
@@ -580,22 +580,22 @@
         <v>13</v>
       </c>
       <c r="E3" t="n">
-        <v>0.640300288344364</v>
+        <v>0.54132298500056</v>
       </c>
       <c r="F3" t="n">
-        <v>0.244413871425249</v>
+        <v>0.21412407002624</v>
       </c>
       <c r="G3" t="n">
-        <v>2.61973792490003</v>
+        <v>2.52808096228613</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0087997364271166</v>
+        <v>0.0114687901264779</v>
       </c>
       <c r="I3" t="n">
-        <v>0.161257903028873</v>
+        <v>0.121647519525997</v>
       </c>
       <c r="J3" t="n">
-        <v>1.11934267365986</v>
+        <v>0.960998450475123</v>
       </c>
     </row>
     <row r="4">
@@ -612,22 +612,22 @@
         <v>13</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.324327878439819</v>
+        <v>-0.24354978697919</v>
       </c>
       <c r="F4" t="n">
-        <v>0.101156751944738</v>
+        <v>0.0929761047922707</v>
       </c>
       <c r="G4" t="n">
-        <v>-3.20619110642264</v>
+        <v>-2.61948795901199</v>
       </c>
       <c r="H4" t="n">
-        <v>0.00134504627369162</v>
+        <v>0.00880618814955902</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.522591469044557</v>
+        <v>-0.425779603794863</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.126064287835081</v>
+        <v>-0.0613199701635178</v>
       </c>
     </row>
     <row r="5">
@@ -644,22 +644,22 @@
         <v>13</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.159872490360079</v>
+        <v>-0.117953434182356</v>
       </c>
       <c r="F5" t="n">
-        <v>0.134641786096087</v>
+        <v>0.120908134256972</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.18739133663889</v>
+        <v>-0.975562437607911</v>
       </c>
       <c r="H5" t="n">
-        <v>0.235073295621143</v>
+        <v>0.329281346340804</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.423765541922555</v>
+        <v>-0.354929022763955</v>
       </c>
       <c r="J5" t="n">
-        <v>0.104020561202396</v>
+        <v>0.119022154399243</v>
       </c>
     </row>
     <row r="6">
@@ -676,22 +676,22 @@
         <v>13</v>
       </c>
       <c r="E6" t="n">
-        <v>0.407573244966622</v>
+        <v>0.368026318514926</v>
       </c>
       <c r="F6" t="n">
-        <v>0.23251781567549</v>
+        <v>0.205138817197166</v>
       </c>
       <c r="G6" t="n">
-        <v>1.75286888784232</v>
+        <v>1.79403549042209</v>
       </c>
       <c r="H6" t="n">
-        <v>0.079624515112216</v>
+        <v>0.0728075043151878</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.048153299521262</v>
+        <v>-0.0340383750226658</v>
       </c>
       <c r="J6" t="n">
-        <v>0.863299789454505</v>
+        <v>0.770091012052518</v>
       </c>
     </row>
     <row r="7">
@@ -708,22 +708,22 @@
         <v>13</v>
       </c>
       <c r="E7" t="n">
-        <v>0.286259699522905</v>
+        <v>0.232940105941685</v>
       </c>
       <c r="F7" t="n">
-        <v>0.152419124555843</v>
+        <v>0.134795759536144</v>
       </c>
       <c r="G7" t="n">
-        <v>1.87810880266555</v>
+        <v>1.7280966904543</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0603662823743948</v>
+        <v>0.0839708907607421</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.0124762951616706</v>
+        <v>-0.0312547280178796</v>
       </c>
       <c r="J7" t="n">
-        <v>0.584995694207481</v>
+        <v>0.49713493990125</v>
       </c>
     </row>
     <row r="8">
@@ -740,22 +740,22 @@
         <v>13</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.147034223002406</v>
+        <v>-0.13513624192657</v>
       </c>
       <c r="F8" t="n">
-        <v>0.177591172069629</v>
+        <v>0.155358614929608</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.827936553877563</v>
+        <v>-0.869834234733615</v>
       </c>
       <c r="H8" t="n">
-        <v>0.407706432100691</v>
+        <v>0.384390999611208</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.495106524231135</v>
+        <v>-0.439633531876629</v>
       </c>
       <c r="J8" t="n">
-        <v>0.201038078226323</v>
+        <v>0.169361048023489</v>
       </c>
     </row>
     <row r="9">
@@ -772,22 +772,22 @@
         <v>13</v>
       </c>
       <c r="E9" t="n">
-        <v>0.388460341437506</v>
+        <v>0.273557477788687</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0466221286466111</v>
+        <v>0.0404599831353316</v>
       </c>
       <c r="G9" t="n">
-        <v>8.33210221656712</v>
+        <v>6.7611861545687</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0000000000000000794193315881139</v>
+        <v>0.000000000013686653058741</v>
       </c>
       <c r="I9" t="n">
-        <v>0.297082648407555</v>
+        <v>0.194257368028339</v>
       </c>
       <c r="J9" t="n">
-        <v>0.479838034467457</v>
+        <v>0.352857587549035</v>
       </c>
     </row>
     <row r="10">
@@ -804,22 +804,22 @@
         <v>13</v>
       </c>
       <c r="E10" t="n">
-        <v>0.244113284779474</v>
+        <v>0.194044172397637</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0912299579398321</v>
+        <v>0.0916209362791603</v>
       </c>
       <c r="G10" t="n">
-        <v>2.67580179024605</v>
+        <v>2.11790208960977</v>
       </c>
       <c r="H10" t="n">
-        <v>0.00745507203093239</v>
+        <v>0.0341833606120209</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0653058529062994</v>
+        <v>0.0144704370606434</v>
       </c>
       <c r="J10" t="n">
-        <v>0.422920716652649</v>
+        <v>0.37361790773463</v>
       </c>
     </row>
     <row r="11">
@@ -836,22 +836,22 @@
         <v>13</v>
       </c>
       <c r="E11" t="n">
-        <v>0.235184673171608</v>
+        <v>0.164165712691586</v>
       </c>
       <c r="F11" t="n">
-        <v>0.267543509783759</v>
+        <v>0.284494725541258</v>
       </c>
       <c r="G11" t="n">
-        <v>0.879052059090109</v>
+        <v>0.577043080075585</v>
       </c>
       <c r="H11" t="n">
-        <v>0.379373049804451</v>
+        <v>0.563910353946242</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.289190970301999</v>
+        <v>-0.393433703160888</v>
       </c>
       <c r="J11" t="n">
-        <v>0.759560316645215</v>
+        <v>0.72176512854406</v>
       </c>
     </row>
     <row r="12">
@@ -868,22 +868,22 @@
         <v>13</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.181169608041696</v>
+        <v>-0.273208615744226</v>
       </c>
       <c r="F12" t="n">
-        <v>0.110304222688766</v>
+        <v>0.112990938030605</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.64245396618119</v>
+        <v>-2.41796926821003</v>
       </c>
       <c r="H12" t="n">
-        <v>0.100495958778184</v>
+        <v>0.0156073949023706</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.397361911854363</v>
+        <v>-0.494666784863608</v>
       </c>
       <c r="J12" t="n">
-        <v>0.0350226957709704</v>
+        <v>-0.0517504466248443</v>
       </c>
     </row>
     <row r="13">
@@ -900,22 +900,22 @@
         <v>13</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.20206056331498</v>
+        <v>-0.292881821978259</v>
       </c>
       <c r="F13" t="n">
-        <v>0.140308596970487</v>
+        <v>0.14617915278187</v>
       </c>
       <c r="G13" t="n">
-        <v>-1.44011534344886</v>
+        <v>-2.0035813343049</v>
       </c>
       <c r="H13" t="n">
-        <v>0.149834768818127</v>
+        <v>0.0451149269882193</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.47706036009848</v>
+        <v>-0.579387696721303</v>
       </c>
       <c r="J13" t="n">
-        <v>0.0729392334685202</v>
+        <v>-0.0063759472352154</v>
       </c>
     </row>
     <row r="14">
@@ -932,22 +932,22 @@
         <v>13</v>
       </c>
       <c r="E14" t="n">
-        <v>0.585843095690204</v>
+        <v>0.454646933343914</v>
       </c>
       <c r="F14" t="n">
-        <v>0.251808184408262</v>
+        <v>0.263036557695387</v>
       </c>
       <c r="G14" t="n">
-        <v>2.3265450925152</v>
+        <v>1.72845530418789</v>
       </c>
       <c r="H14" t="n">
-        <v>0.0199894898216336</v>
+        <v>0.0839066276632658</v>
       </c>
       <c r="I14" t="n">
-        <v>0.0923081232375901</v>
+        <v>-0.0608952463564351</v>
       </c>
       <c r="J14" t="n">
-        <v>1.07937806814282</v>
+        <v>0.970189113044264</v>
       </c>
     </row>
     <row r="15">
@@ -964,22 +964,22 @@
         <v>13</v>
       </c>
       <c r="E15" t="n">
-        <v>0.355594893211605</v>
+        <v>0.351882404475552</v>
       </c>
       <c r="F15" t="n">
-        <v>0.185174033163551</v>
+        <v>0.190481854218573</v>
       </c>
       <c r="G15" t="n">
-        <v>1.92032806725948</v>
+        <v>1.84732769385883</v>
       </c>
       <c r="H15" t="n">
-        <v>0.054816473256671</v>
+        <v>0.0646996615820745</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.00733954266098014</v>
+        <v>-0.0214551695012611</v>
       </c>
       <c r="J15" t="n">
-        <v>0.718529329084189</v>
+        <v>0.725219978452364</v>
       </c>
     </row>
     <row r="16">
@@ -996,22 +996,22 @@
         <v>13</v>
       </c>
       <c r="E16" t="n">
-        <v>0.251082348178222</v>
+        <v>0.292486531027443</v>
       </c>
       <c r="F16" t="n">
-        <v>0.21816882218881</v>
+        <v>0.216815047876698</v>
       </c>
       <c r="G16" t="n">
-        <v>1.15086264691354</v>
+        <v>1.34901398169457</v>
       </c>
       <c r="H16" t="n">
-        <v>0.24978874692377</v>
+        <v>0.177332475215482</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.176520685861368</v>
+        <v>-0.132463154117212</v>
       </c>
       <c r="J16" t="n">
-        <v>0.678685382217812</v>
+        <v>0.717436216172098</v>
       </c>
     </row>
     <row r="17">
@@ -1028,22 +1028,22 @@
         <v>13</v>
       </c>
       <c r="E17" t="n">
-        <v>0.261490337102811</v>
+        <v>0.292743724347569</v>
       </c>
       <c r="F17" t="n">
-        <v>0.0491326230022274</v>
+        <v>0.061471085450134</v>
       </c>
       <c r="G17" t="n">
-        <v>5.32213265086533</v>
+        <v>4.76229957880027</v>
       </c>
       <c r="H17" t="n">
-        <v>0.000000102557740359987</v>
+        <v>0.00000191399255722891</v>
       </c>
       <c r="I17" t="n">
-        <v>0.165192165552462</v>
+        <v>0.172262610774722</v>
       </c>
       <c r="J17" t="n">
-        <v>0.357788508653161</v>
+        <v>0.413224837920415</v>
       </c>
     </row>
     <row r="18">
@@ -1060,22 +1060,22 @@
         <v>13</v>
       </c>
       <c r="E18" t="n">
-        <v>0.374037816454783</v>
+        <v>0.205161038753211</v>
       </c>
       <c r="F18" t="n">
-        <v>0.129954792871143</v>
+        <v>0.119737667778261</v>
       </c>
       <c r="G18" t="n">
-        <v>2.87821486373082</v>
+        <v>1.71342103583596</v>
       </c>
       <c r="H18" t="n">
-        <v>0.00399932641059027</v>
+        <v>0.0866351090373105</v>
       </c>
       <c r="I18" t="n">
-        <v>0.11933110280898</v>
+        <v>-0.0295204776850038</v>
       </c>
       <c r="J18" t="n">
-        <v>0.628744530100585</v>
+        <v>0.439842555191425</v>
       </c>
     </row>
     <row r="19">
@@ -1092,22 +1092,22 @@
         <v>13</v>
       </c>
       <c r="E19" t="n">
-        <v>0.129001462397835</v>
+        <v>-0.0733965693584984</v>
       </c>
       <c r="F19" t="n">
-        <v>0.37403015093157</v>
+        <v>0.346185238344782</v>
       </c>
       <c r="G19" t="n">
-        <v>0.344895891618739</v>
+        <v>-0.212015306341281</v>
       </c>
       <c r="H19" t="n">
-        <v>0.730172639338448</v>
+        <v>0.832095093031392</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.604084162560123</v>
+        <v>-0.751907168493686</v>
       </c>
       <c r="J19" t="n">
-        <v>0.862087087355794</v>
+        <v>0.605114029776689</v>
       </c>
     </row>
     <row r="20">
@@ -1124,22 +1124,22 @@
         <v>13</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.241426402382246</v>
+        <v>0.0551586342776503</v>
       </c>
       <c r="F20" t="n">
-        <v>0.129553082405235</v>
+        <v>0.121005686649762</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.8635326763363</v>
+        <v>0.455835058705144</v>
       </c>
       <c r="H20" t="n">
-        <v>0.062387359633937</v>
+        <v>0.64850859142644</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.495345777982656</v>
+        <v>-0.182008153480422</v>
       </c>
       <c r="J20" t="n">
-        <v>0.0124929732181649</v>
+        <v>0.292325422035722</v>
       </c>
     </row>
     <row r="21">
@@ -1156,22 +1156,22 @@
         <v>13</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.455094112723997</v>
+        <v>-0.133378543141746</v>
       </c>
       <c r="F21" t="n">
-        <v>0.162872281833065</v>
+        <v>0.149922376495592</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.79417779134723</v>
+        <v>-0.889650672964535</v>
       </c>
       <c r="H21" t="n">
-        <v>0.00520318634722789</v>
+        <v>0.373653488061566</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.774317919196661</v>
+        <v>-0.427221001549762</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.135870306251332</v>
+        <v>0.160463915266269</v>
       </c>
     </row>
     <row r="22">
@@ -1188,22 +1188,22 @@
         <v>13</v>
       </c>
       <c r="E22" t="n">
-        <v>1.13057444887298</v>
+        <v>0.758331880124282</v>
       </c>
       <c r="F22" t="n">
-        <v>0.351649534584316</v>
+        <v>0.31379843310359</v>
       </c>
       <c r="G22" t="n">
-        <v>3.21506027360289</v>
+        <v>2.41662099018176</v>
       </c>
       <c r="H22" t="n">
-        <v>0.00130417135362369</v>
+        <v>0.015665319068008</v>
       </c>
       <c r="I22" t="n">
-        <v>0.441354025907448</v>
+        <v>0.143298252836144</v>
       </c>
       <c r="J22" t="n">
-        <v>1.81979487183851</v>
+        <v>1.37336550741242</v>
       </c>
     </row>
     <row r="23">
@@ -1220,22 +1220,22 @@
         <v>13</v>
       </c>
       <c r="E23" t="n">
-        <v>0.219673857206496</v>
+        <v>-0.0102117486020833</v>
       </c>
       <c r="F23" t="n">
-        <v>0.213010415224432</v>
+        <v>0.198309411455962</v>
       </c>
       <c r="G23" t="n">
-        <v>1.03128223554254</v>
+        <v>-0.0514940190034855</v>
       </c>
       <c r="H23" t="n">
-        <v>0.302408486382207</v>
+        <v>0.958931867674259</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.197818884965313</v>
+        <v>-0.398891052851103</v>
       </c>
       <c r="J23" t="n">
-        <v>0.637166599378306</v>
+        <v>0.378467555646936</v>
       </c>
     </row>
     <row r="24">
@@ -1252,22 +1252,22 @@
         <v>13</v>
       </c>
       <c r="E24" t="n">
-        <v>0.2081502047498</v>
+        <v>0.0942493352648385</v>
       </c>
       <c r="F24" t="n">
-        <v>0.236486143019286</v>
+        <v>0.207877637107203</v>
       </c>
       <c r="G24" t="n">
-        <v>0.880179287007207</v>
+        <v>0.45338852498229</v>
       </c>
       <c r="H24" t="n">
-        <v>0.378762192433627</v>
+        <v>0.650268997884794</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.25535411841079</v>
+        <v>-0.313183346656566</v>
       </c>
       <c r="J24" t="n">
-        <v>0.67165452791039</v>
+        <v>0.501682017186243</v>
       </c>
     </row>
     <row r="25">
@@ -1284,22 +1284,22 @@
         <v>13</v>
       </c>
       <c r="E25" t="n">
-        <v>0.34747293895913</v>
+        <v>0.516528398787738</v>
       </c>
       <c r="F25" t="n">
-        <v>0.0840566480103321</v>
+        <v>0.0796364216961293</v>
       </c>
       <c r="G25" t="n">
-        <v>4.1337948536375</v>
+        <v>6.48608247063974</v>
       </c>
       <c r="H25" t="n">
-        <v>0.0000356822003466374</v>
+        <v>0.0000000000880969564312911</v>
       </c>
       <c r="I25" t="n">
-        <v>0.182724936197718</v>
+        <v>0.360443880405681</v>
       </c>
       <c r="J25" t="n">
-        <v>0.512220941720541</v>
+        <v>0.672612917169796</v>
       </c>
     </row>
     <row r="26">
@@ -1316,22 +1316,22 @@
         <v>13</v>
       </c>
       <c r="E26" t="n">
-        <v>0.0838646551160669</v>
+        <v>0.0820421492177339</v>
       </c>
       <c r="F26" t="n">
-        <v>0.0496438640427079</v>
+        <v>0.0496994551071046</v>
       </c>
       <c r="G26" t="n">
-        <v>1.68932569479119</v>
+        <v>1.65076556756869</v>
       </c>
       <c r="H26" t="n">
-        <v>0.091157031917844</v>
+        <v>0.0987864535173949</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.0134355304610436</v>
+        <v>-0.0153669928434563</v>
       </c>
       <c r="J26" t="n">
-        <v>0.181164840693177</v>
+        <v>0.179451291278924</v>
       </c>
     </row>
     <row r="27">
@@ -1348,22 +1348,22 @@
         <v>13</v>
       </c>
       <c r="E27" t="n">
-        <v>0.269276899793842</v>
+        <v>0.0878639189106702</v>
       </c>
       <c r="F27" t="n">
-        <v>0.0998756083471291</v>
+        <v>0.122597792035889</v>
       </c>
       <c r="G27" t="n">
-        <v>2.69612274959006</v>
+        <v>0.716684350114145</v>
       </c>
       <c r="H27" t="n">
-        <v>0.00701518100779991</v>
+        <v>0.473568884493641</v>
       </c>
       <c r="I27" t="n">
-        <v>0.0735243044994407</v>
+        <v>-0.152423338063804</v>
       </c>
       <c r="J27" t="n">
-        <v>0.465029495088243</v>
+        <v>0.328151175885144</v>
       </c>
     </row>
     <row r="28">
@@ -1380,22 +1380,22 @@
         <v>13</v>
       </c>
       <c r="E28" t="n">
-        <v>0.23812932662772</v>
+        <v>0.113159597327033</v>
       </c>
       <c r="F28" t="n">
-        <v>0.318352112301691</v>
+        <v>0.381245949454255</v>
       </c>
       <c r="G28" t="n">
-        <v>0.748006114694956</v>
+        <v>0.296815212040988</v>
       </c>
       <c r="H28" t="n">
-        <v>0.454456469303091</v>
+        <v>0.76660759103759</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.385829347885845</v>
+        <v>-0.634068732855085</v>
       </c>
       <c r="J28" t="n">
-        <v>0.862088001141285</v>
+        <v>0.86038792750915</v>
       </c>
     </row>
     <row r="29">
@@ -1412,22 +1412,22 @@
         <v>13</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.155723283633436</v>
+        <v>-0.0678673742881257</v>
       </c>
       <c r="F29" t="n">
-        <v>0.115097808563214</v>
+        <v>0.128018914666718</v>
       </c>
       <c r="G29" t="n">
-        <v>-1.35296480078429</v>
+        <v>-0.530135523057746</v>
       </c>
       <c r="H29" t="n">
-        <v>0.176066875696063</v>
+        <v>0.596017971225274</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.381310843116821</v>
+        <v>-0.3187798363748</v>
       </c>
       <c r="J29" t="n">
-        <v>0.0698642758499483</v>
+        <v>0.183045087798549</v>
       </c>
     </row>
     <row r="30">
@@ -1444,22 +1444,22 @@
         <v>13</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.228848782864791</v>
+        <v>-0.0749270285936793</v>
       </c>
       <c r="F30" t="n">
-        <v>0.149237186180081</v>
+        <v>0.16958872129383</v>
       </c>
       <c r="G30" t="n">
-        <v>-1.53345683286098</v>
+        <v>-0.441816106767268</v>
       </c>
       <c r="H30" t="n">
-        <v>0.125163334844745</v>
+        <v>0.658622282222644</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.521348292931849</v>
+        <v>-0.407314814513787</v>
       </c>
       <c r="J30" t="n">
-        <v>0.0636507272022666</v>
+        <v>0.257460757326429</v>
       </c>
     </row>
     <row r="31">
@@ -1476,22 +1476,22 @@
         <v>13</v>
       </c>
       <c r="E31" t="n">
-        <v>0.348517890993122</v>
+        <v>-0.188079423847452</v>
       </c>
       <c r="F31" t="n">
-        <v>0.314205018821345</v>
+        <v>0.394296935087054</v>
       </c>
       <c r="G31" t="n">
-        <v>1.10920535992866</v>
+        <v>-0.476999456782303</v>
       </c>
       <c r="H31" t="n">
-        <v>0.267341600889275</v>
+        <v>0.633362508456308</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.267312629658443</v>
+        <v>-0.960887215832605</v>
       </c>
       <c r="J31" t="n">
-        <v>0.964348411644688</v>
+        <v>0.584728368137702</v>
       </c>
     </row>
     <row r="32">
@@ -1508,22 +1508,22 @@
         <v>13</v>
       </c>
       <c r="E32" t="n">
-        <v>0.420186100562519</v>
+        <v>0.264477342724727</v>
       </c>
       <c r="F32" t="n">
-        <v>0.181691816063456</v>
+        <v>0.211252570338046</v>
       </c>
       <c r="G32" t="n">
-        <v>2.31263085848495</v>
+        <v>1.25194851973403</v>
       </c>
       <c r="H32" t="n">
-        <v>0.0207429434102839</v>
+        <v>0.210588623221776</v>
       </c>
       <c r="I32" t="n">
-        <v>0.0640766847924694</v>
+        <v>-0.149570086779358</v>
       </c>
       <c r="J32" t="n">
-        <v>0.776295516332569</v>
+        <v>0.678524772228812</v>
       </c>
     </row>
     <row r="33">
@@ -1540,22 +1540,22 @@
         <v>13</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.0821809564904767</v>
+        <v>-0.181118361811929</v>
       </c>
       <c r="F33" t="n">
-        <v>0.183440695908195</v>
+        <v>0.206934201436906</v>
       </c>
       <c r="G33" t="n">
-        <v>-0.447997409100568</v>
+        <v>-0.875246143722413</v>
       </c>
       <c r="H33" t="n">
-        <v>0.654155066464561</v>
+        <v>0.381439990867892</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.441718113769504</v>
+        <v>-0.58670194379782</v>
       </c>
       <c r="J33" t="n">
-        <v>0.27735620078855</v>
+        <v>0.224465220173963</v>
       </c>
     </row>
     <row r="34">
@@ -1572,22 +1572,22 @@
         <v>13</v>
       </c>
       <c r="E34" t="n">
-        <v>0.0444565033029176</v>
+        <v>0.0524681051587884</v>
       </c>
       <c r="F34" t="n">
-        <v>0.06276832887796</v>
+        <v>0.0632541274801786</v>
       </c>
       <c r="G34" t="n">
-        <v>0.7082632929316</v>
+        <v>0.829481130306159</v>
       </c>
       <c r="H34" t="n">
-        <v>0.478781767671716</v>
+        <v>0.406832210020915</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.0785671606676493</v>
+        <v>-0.0715077065758669</v>
       </c>
       <c r="J34" t="n">
-        <v>0.167480167273485</v>
+        <v>0.176443916893444</v>
       </c>
     </row>
     <row r="35">
@@ -1604,22 +1604,22 @@
         <v>13</v>
       </c>
       <c r="E35" t="n">
-        <v>0.192227774619259</v>
+        <v>0.252538420976138</v>
       </c>
       <c r="F35" t="n">
-        <v>0.0649951695152916</v>
+        <v>0.0778397307751656</v>
       </c>
       <c r="G35" t="n">
-        <v>2.95757017102683</v>
+        <v>3.24433831490986</v>
       </c>
       <c r="H35" t="n">
-        <v>0.00310074164750225</v>
+        <v>0.00117723830665639</v>
       </c>
       <c r="I35" t="n">
-        <v>0.0648395832002115</v>
+        <v>0.0999753520905194</v>
       </c>
       <c r="J35" t="n">
-        <v>0.319615966038306</v>
+        <v>0.405101489861757</v>
       </c>
     </row>
     <row r="36">
@@ -1636,22 +1636,22 @@
         <v>13</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.0378251810439071</v>
+        <v>0.0314916029118364</v>
       </c>
       <c r="F36" t="n">
-        <v>0.14075798155288</v>
+        <v>0.122905859988017</v>
       </c>
       <c r="G36" t="n">
-        <v>-0.268724946369716</v>
+        <v>0.256225398161705</v>
       </c>
       <c r="H36" t="n">
-        <v>0.788141353252743</v>
+        <v>0.797776798171825</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.313705755424104</v>
+        <v>-0.209399456153599</v>
       </c>
       <c r="J36" t="n">
-        <v>0.23805539333629</v>
+        <v>0.272382661977272</v>
       </c>
     </row>
     <row r="37">
@@ -1668,22 +1668,22 @@
         <v>13</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.142928479547019</v>
+        <v>-0.133916467962092</v>
       </c>
       <c r="F37" t="n">
-        <v>0.176089445450629</v>
+        <v>0.158178690667461</v>
       </c>
       <c r="G37" t="n">
-        <v>-0.811681127061599</v>
+        <v>-0.846615099650963</v>
       </c>
       <c r="H37" t="n">
-        <v>0.416974626489011</v>
+        <v>0.397209694790398</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.488057450687882</v>
+        <v>-0.443941004792018</v>
       </c>
       <c r="J37" t="n">
-        <v>0.202200491593845</v>
+        <v>0.176108068867835</v>
       </c>
     </row>
     <row r="38">
@@ -1700,22 +1700,22 @@
         <v>13</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.0777334006102046</v>
+        <v>-0.0679048469322782</v>
       </c>
       <c r="F38" t="n">
-        <v>0.0546425853743479</v>
+        <v>0.0624976020526571</v>
       </c>
       <c r="G38" t="n">
-        <v>-1.42257911256697</v>
+        <v>-1.08651923757115</v>
       </c>
       <c r="H38" t="n">
-        <v>0.154858202590725</v>
+        <v>0.277249334486533</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.184830899966082</v>
+        <v>-0.190397896075603</v>
       </c>
       <c r="J38" t="n">
-        <v>0.0293640987456724</v>
+        <v>0.0545882022110463</v>
       </c>
     </row>
     <row r="39">
@@ -1732,22 +1732,22 @@
         <v>13</v>
       </c>
       <c r="E39" t="n">
-        <v>0.423096674060706</v>
+        <v>0.668198152897988</v>
       </c>
       <c r="F39" t="n">
-        <v>0.0777989751574755</v>
+        <v>0.101641500360496</v>
       </c>
       <c r="G39" t="n">
-        <v>5.43833223001076</v>
+        <v>6.57406817616881</v>
       </c>
       <c r="H39" t="n">
-        <v>0.0000000537816188577631</v>
+        <v>0.0000000000489587965936197</v>
       </c>
       <c r="I39" t="n">
-        <v>0.270613484717927</v>
+        <v>0.468984472856801</v>
       </c>
       <c r="J39" t="n">
-        <v>0.575579863403484</v>
+        <v>0.867411832939176</v>
       </c>
     </row>
     <row r="40">
@@ -1764,22 +1764,22 @@
         <v>30</v>
       </c>
       <c r="E40" t="n">
-        <v>0.010858650002881</v>
+        <v>0.0022773281121768</v>
       </c>
       <c r="F40" t="n">
-        <v>0.0190800177660233</v>
+        <v>0.0155451644170678</v>
       </c>
       <c r="G40" t="n">
-        <v>0.56911110545282</v>
+        <v>0.14649752495872</v>
       </c>
       <c r="H40" t="n">
-        <v>0.569280742278157</v>
+        <v>0.883528643637613</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.0265374976429091</v>
+        <v>-0.0281906342790297</v>
       </c>
       <c r="J40" t="n">
-        <v>0.048254797648671</v>
+        <v>0.0327452905033833</v>
       </c>
     </row>
     <row r="41">
@@ -1796,22 +1796,22 @@
         <v>31</v>
       </c>
       <c r="E41" t="n">
-        <v>0.482598637377756</v>
+        <v>0.729835595846015</v>
       </c>
       <c r="F41" t="n">
-        <v>0.11209530834559</v>
+        <v>0.134782019730613</v>
       </c>
       <c r="G41" t="n">
-        <v>4.3052527755212</v>
+        <v>5.41493292135499</v>
       </c>
       <c r="H41" t="n">
-        <v>0.0000166795170409535</v>
+        <v>0.0000000613116865778788</v>
       </c>
       <c r="I41" t="n">
-        <v>0.262895870184488</v>
+        <v>0.465667691410447</v>
       </c>
       <c r="J41" t="n">
-        <v>0.702301404571025</v>
+        <v>0.994003500281584</v>
       </c>
     </row>
     <row r="42">
@@ -1828,22 +1828,22 @@
         <v>32</v>
       </c>
       <c r="E42" t="n">
-        <v>-0.021722164025745</v>
+        <v>-0.0130327075015359</v>
       </c>
       <c r="F42" t="n">
-        <v>0.0243300864308966</v>
+        <v>0.0169559743701578</v>
       </c>
       <c r="G42" t="n">
-        <v>-0.892810803917251</v>
+        <v>-0.768620382233725</v>
       </c>
       <c r="H42" t="n">
-        <v>0.371958499631885</v>
+        <v>0.442118702048286</v>
       </c>
       <c r="I42" t="n">
-        <v>-0.0694082571710489</v>
+        <v>-0.0462658065898294</v>
       </c>
       <c r="J42" t="n">
-        <v>0.025963929119559</v>
+        <v>0.0202003915867576</v>
       </c>
     </row>
     <row r="43">
@@ -1860,22 +1860,22 @@
         <v>34</v>
       </c>
       <c r="E43" t="n">
-        <v>0.473071607313337</v>
+        <v>0.349467756876472</v>
       </c>
       <c r="F43" t="n">
-        <v>0.0790340352876879</v>
+        <v>0.0629122348706135</v>
       </c>
       <c r="G43" t="n">
-        <v>5.98566940927832</v>
+        <v>5.55484569249836</v>
       </c>
       <c r="H43" t="n">
-        <v>0.00000000215501685490133</v>
+        <v>0.0000000277857106464949</v>
       </c>
       <c r="I43" t="n">
-        <v>0.318167744596601</v>
+        <v>0.226162042343145</v>
       </c>
       <c r="J43" t="n">
-        <v>0.627975470030073</v>
+        <v>0.4727734714098</v>
       </c>
     </row>
     <row r="44">
@@ -1892,22 +1892,22 @@
         <v>36</v>
       </c>
       <c r="E44" t="n">
-        <v>-0.514277312975856</v>
+        <v>-0.31706982422805</v>
       </c>
       <c r="F44" t="n">
-        <v>0.0949201668750428</v>
+        <v>0.0786108396380663</v>
       </c>
       <c r="G44" t="n">
-        <v>-5.41799840757627</v>
+        <v>-4.03341098616778</v>
       </c>
       <c r="H44" t="n">
-        <v>0.0000000602699528748556</v>
+        <v>0.0000549730102984767</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.700317421457472</v>
+        <v>-0.471144238713113</v>
       </c>
       <c r="J44" t="n">
-        <v>-0.32823720449424</v>
+        <v>-0.162995409742986</v>
       </c>
     </row>
     <row r="45">
@@ -1924,22 +1924,22 @@
         <v>13</v>
       </c>
       <c r="E45" t="n">
-        <v>-0.0145027969008119</v>
+        <v>-0.176770407939905</v>
       </c>
       <c r="F45" t="n">
-        <v>0.0751328016442454</v>
+        <v>0.0848149738872519</v>
       </c>
       <c r="G45" t="n">
-        <v>-0.193028831394879</v>
+        <v>-2.08418867374638</v>
       </c>
       <c r="H45" t="n">
-        <v>0.846936388502208</v>
+        <v>0.0371430085983817</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.161760382181125</v>
+        <v>-0.343004702108624</v>
       </c>
       <c r="J45" t="n">
-        <v>0.132754788379501</v>
+        <v>-0.0105361137711864</v>
       </c>
     </row>
     <row r="46">
@@ -1956,22 +1956,22 @@
         <v>13</v>
       </c>
       <c r="E46" t="n">
-        <v>0.0523016786313598</v>
+        <v>-0.128593310252833</v>
       </c>
       <c r="F46" t="n">
-        <v>0.0396036427152824</v>
+        <v>0.0545336805486331</v>
       </c>
       <c r="G46" t="n">
-        <v>1.32062797877877</v>
+        <v>-2.35805302262982</v>
       </c>
       <c r="H46" t="n">
-        <v>0.186625439036862</v>
+        <v>0.0183710687399331</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.0253200347471858</v>
+        <v>-0.235477360072567</v>
       </c>
       <c r="J46" t="n">
-        <v>0.129923392009905</v>
+        <v>-0.0217092604330998</v>
       </c>
     </row>
     <row r="47">
@@ -1988,22 +1988,22 @@
         <v>39</v>
       </c>
       <c r="E47" t="n">
-        <v>0.37754438259507</v>
+        <v>0.862891958941376</v>
       </c>
       <c r="F47" t="n">
-        <v>0.0999245052724578</v>
+        <v>0.186569029561831</v>
       </c>
       <c r="G47" t="n">
-        <v>3.77829624040313</v>
+        <v>4.6250546565415</v>
       </c>
       <c r="H47" t="n">
-        <v>0.000157904974577415</v>
+        <v>0.0000037449963405347</v>
       </c>
       <c r="I47" t="n">
-        <v>0.18169595108807</v>
+        <v>0.497223380369598</v>
       </c>
       <c r="J47" t="n">
-        <v>0.573392814102069</v>
+        <v>1.22856053751315</v>
       </c>
     </row>
     <row r="48">
@@ -2020,22 +2020,22 @@
         <v>40</v>
       </c>
       <c r="E48" t="n">
-        <v>-0.0603921060527264</v>
+        <v>-0.0826772817701602</v>
       </c>
       <c r="F48" t="n">
-        <v>0.0254637359014548</v>
+        <v>0.0209035466836706</v>
       </c>
       <c r="G48" t="n">
-        <v>-2.37169071680782</v>
+        <v>-3.95517961718649</v>
       </c>
       <c r="H48" t="n">
-        <v>0.0177069057238676</v>
+        <v>0.0000764771725143188</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.110300111331417</v>
+        <v>-0.123647480419306</v>
       </c>
       <c r="J48" t="n">
-        <v>-0.0104841007740354</v>
+        <v>-0.0417070831210141</v>
       </c>
     </row>
     <row r="49">
@@ -2052,22 +2052,22 @@
         <v>41</v>
       </c>
       <c r="E49" t="n">
-        <v>0.126989943610134</v>
+        <v>0.0526917141588</v>
       </c>
       <c r="F49" t="n">
-        <v>0.0738348631653696</v>
+        <v>0.0823477806915734</v>
       </c>
       <c r="G49" t="n">
-        <v>1.71991845269235</v>
+        <v>0.63986805371419</v>
       </c>
       <c r="H49" t="n">
-        <v>0.0854472657991272</v>
+        <v>0.522258384524319</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.0177237289974333</v>
+        <v>-0.108706970203487</v>
       </c>
       <c r="J49" t="n">
-        <v>0.271703616217702</v>
+        <v>0.214090398521087</v>
       </c>
     </row>
     <row r="50">
@@ -2084,22 +2084,22 @@
         <v>42</v>
       </c>
       <c r="E50" t="n">
-        <v>-0.136217178096331</v>
+        <v>-0.0557932338001043</v>
       </c>
       <c r="F50" t="n">
-        <v>0.0680047016236256</v>
+        <v>0.0754446689243955</v>
       </c>
       <c r="G50" t="n">
-        <v>-2.00305530123828</v>
+        <v>-0.739525199003998</v>
       </c>
       <c r="H50" t="n">
-        <v>0.0451713530204275</v>
+        <v>0.459588144005088</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.269503944058029</v>
+        <v>-0.203662067717468</v>
       </c>
       <c r="J50" t="n">
-        <v>-0.0029304121346321</v>
+        <v>0.092075600117259</v>
       </c>
     </row>
     <row r="51">
@@ -2116,22 +2116,22 @@
         <v>44</v>
       </c>
       <c r="E51" t="n">
-        <v>0.0745805132902897</v>
+        <v>0.103213699424901</v>
       </c>
       <c r="F51" t="n">
-        <v>0.064349676669923</v>
+        <v>0.0663257111300954</v>
       </c>
       <c r="G51" t="n">
-        <v>1.15898815891252</v>
+        <v>1.55616423354212</v>
       </c>
       <c r="H51" t="n">
-        <v>0.24646101168506</v>
+        <v>0.119669043951102</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.0515425353995567</v>
+        <v>-0.0267823056390935</v>
       </c>
       <c r="J51" t="n">
-        <v>0.200703561980136</v>
+        <v>0.233209704488895</v>
       </c>
     </row>
     <row r="52">
@@ -2148,22 +2148,22 @@
         <v>46</v>
       </c>
       <c r="E52" t="n">
-        <v>-0.106359799932383</v>
+        <v>-0.276713427102248</v>
       </c>
       <c r="F52" t="n">
-        <v>0.0477045201832616</v>
+        <v>0.082548102257713</v>
       </c>
       <c r="G52" t="n">
-        <v>-2.22955391907919</v>
+        <v>-3.35214765129738</v>
       </c>
       <c r="H52" t="n">
-        <v>0.0257770719600634</v>
+        <v>0.000801872404017824</v>
       </c>
       <c r="I52" t="n">
-        <v>-0.19985894139134</v>
+        <v>-0.438504734519495</v>
       </c>
       <c r="J52" t="n">
-        <v>-0.0128606584734264</v>
+        <v>-0.114922119685001</v>
       </c>
     </row>
     <row r="53">
@@ -2180,22 +2180,22 @@
         <v>48</v>
       </c>
       <c r="E53" t="n">
-        <v>-0.190368597542518</v>
+        <v>-0.308958208147727</v>
       </c>
       <c r="F53" t="n">
-        <v>0.0439695643336465</v>
+        <v>0.0634293674580193</v>
       </c>
       <c r="G53" t="n">
-        <v>-4.32955387271925</v>
+        <v>-4.87090161118525</v>
       </c>
       <c r="H53" t="n">
-        <v>0.0000149411717229988</v>
+        <v>0.00000111090151463368</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.276547360052382</v>
+        <v>-0.433277483927602</v>
       </c>
       <c r="J53" t="n">
-        <v>-0.104189835032654</v>
+        <v>-0.184638932367853</v>
       </c>
     </row>
     <row r="54">
@@ -2212,22 +2212,22 @@
         <v>13</v>
       </c>
       <c r="E54" t="n">
-        <v>3.27994510016124</v>
+        <v>3.30163572234629</v>
       </c>
       <c r="F54" t="n">
-        <v>0.136044198178496</v>
+        <v>0.136210109127464</v>
       </c>
       <c r="G54" t="n">
-        <v>24.1094081487975</v>
+        <v>24.2392854942701</v>
       </c>
       <c r="H54" t="n">
-        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000199173219796548</v>
+        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000857731214422184</v>
       </c>
       <c r="I54" t="n">
-        <v>3.01330337142576</v>
+        <v>3.03466881412619</v>
       </c>
       <c r="J54" t="n">
-        <v>3.54658682889672</v>
+        <v>3.56860263056639</v>
       </c>
     </row>
     <row r="55">
@@ -2244,22 +2244,22 @@
         <v>13</v>
       </c>
       <c r="E55" t="n">
-        <v>1.12065917713749</v>
+        <v>1.12485084600418</v>
       </c>
       <c r="F55" t="n">
-        <v>0.148050190103951</v>
+        <v>0.148067769823949</v>
       </c>
       <c r="G55" t="n">
-        <v>7.56945449614507</v>
+        <v>7.5968649176091</v>
       </c>
       <c r="H55" t="n">
-        <v>0.0000000000000374794714634545</v>
+        <v>0.0000000000000303390937124167</v>
       </c>
       <c r="I55" t="n">
-        <v>0.830486136629435</v>
+        <v>0.834643349878072</v>
       </c>
       <c r="J55" t="n">
-        <v>1.41083221764554</v>
+        <v>1.41505834213029</v>
       </c>
     </row>
     <row r="56">
@@ -2276,22 +2276,22 @@
         <v>13</v>
       </c>
       <c r="E56" t="n">
-        <v>-1.58315104517961</v>
+        <v>-1.57857587194433</v>
       </c>
       <c r="F56" t="n">
-        <v>0.135790125116855</v>
+        <v>0.135814091018978</v>
       </c>
       <c r="G56" t="n">
-        <v>-11.6588083545635</v>
+        <v>-11.6230639994767</v>
       </c>
       <c r="H56" t="n">
-        <v>0.000000000000000000000000000000206917964700729</v>
+        <v>0.000000000000000000000000000000314645626323752</v>
       </c>
       <c r="I56" t="n">
-        <v>-1.84929479986484</v>
+        <v>-1.84476659893458</v>
       </c>
       <c r="J56" t="n">
-        <v>-1.31700729049439</v>
+        <v>-1.31238514495409</v>
       </c>
     </row>
     <row r="57">
@@ -2308,22 +2308,22 @@
         <v>13</v>
       </c>
       <c r="E57" t="n">
-        <v>-1.19618271731683</v>
+        <v>-1.19583763533843</v>
       </c>
       <c r="F57" t="n">
-        <v>0.17260301456533</v>
+        <v>0.172425076433085</v>
       </c>
       <c r="G57" t="n">
-        <v>-6.93025391433173</v>
+        <v>-6.93540440912903</v>
       </c>
       <c r="H57" t="n">
-        <v>0.00000000000420085926717674</v>
+        <v>0.00000000000405060717803447</v>
       </c>
       <c r="I57" t="n">
-        <v>-1.53447840948792</v>
+        <v>-1.53378457517884</v>
       </c>
       <c r="J57" t="n">
-        <v>-0.857887025145744</v>
+        <v>-0.857890695498017</v>
       </c>
     </row>
     <row r="58">
@@ -2340,22 +2340,22 @@
         <v>13</v>
       </c>
       <c r="E58" t="n">
-        <v>-0.22131528881855</v>
+        <v>-0.218546552914525</v>
       </c>
       <c r="F58" t="n">
-        <v>0.21473072465742</v>
+        <v>0.214530728422761</v>
       </c>
       <c r="G58" t="n">
-        <v>-1.03066428510235</v>
+        <v>-1.01871911087651</v>
       </c>
       <c r="H58" t="n">
-        <v>0.302698278542378</v>
+        <v>0.308336337066487</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.64217977552128</v>
+        <v>-0.639019054200281</v>
       </c>
       <c r="J58" t="n">
-        <v>0.19954919788418</v>
+        <v>0.20192594837123</v>
       </c>
     </row>
     <row r="59">
@@ -2372,22 +2372,22 @@
         <v>13</v>
       </c>
       <c r="E59" t="n">
-        <v>0.705817263244807</v>
+        <v>0.705817526854793</v>
       </c>
       <c r="F59" t="n">
-        <v>0.0218414912080004</v>
+        <v>0.0218414901992416</v>
       </c>
       <c r="G59" t="n">
-        <v>32.3154338008878</v>
+        <v>32.3154473626209</v>
       </c>
       <c r="H59" t="n">
-        <v>4.246367116313e-229</v>
+        <v>4.24450476141703e-229</v>
       </c>
       <c r="I59" t="n">
-        <v>0.663008727108478</v>
+        <v>0.663008992695594</v>
       </c>
       <c r="J59" t="n">
-        <v>0.748625799381136</v>
+        <v>0.748626061013991</v>
       </c>
     </row>
     <row r="60">
@@ -2404,22 +2404,22 @@
         <v>13</v>
       </c>
       <c r="E60" t="n">
-        <v>0.427487516905115</v>
+        <v>0.427487311624608</v>
       </c>
       <c r="F60" t="n">
-        <v>0.0543255726102316</v>
+        <v>0.0543255348009999</v>
       </c>
       <c r="G60" t="n">
-        <v>7.86899237992759</v>
+        <v>7.86899407784091</v>
       </c>
       <c r="H60" t="n">
-        <v>0.00000000000000357508946754797</v>
+        <v>0.00000000000000357504095328369</v>
       </c>
       <c r="I60" t="n">
-        <v>0.321011351149546</v>
+        <v>0.321011219973771</v>
       </c>
       <c r="J60" t="n">
-        <v>0.533963682660685</v>
+        <v>0.533963403275445</v>
       </c>
     </row>
     <row r="61">
@@ -2436,22 +2436,22 @@
         <v>13</v>
       </c>
       <c r="E61" t="n">
-        <v>0.03000088704211</v>
+        <v>0.0300006795489007</v>
       </c>
       <c r="F61" t="n">
-        <v>0.0254345329672875</v>
+        <v>0.0254345214919959</v>
       </c>
       <c r="G61" t="n">
-        <v>1.17953363172406</v>
+        <v>1.17952600595776</v>
       </c>
       <c r="H61" t="n">
-        <v>0.238185752851383</v>
+        <v>0.238188787501594</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.0198498815373702</v>
+        <v>-0.0198500665394211</v>
       </c>
       <c r="J61" t="n">
-        <v>0.0798516556215901</v>
+        <v>0.0798514256372225</v>
       </c>
     </row>
     <row r="62">
@@ -2468,22 +2468,22 @@
         <v>13</v>
       </c>
       <c r="E62" t="n">
-        <v>-0.0504308904185562</v>
+        <v>-0.0504314204485048</v>
       </c>
       <c r="F62" t="n">
-        <v>0.0279505800604274</v>
+        <v>0.0279505020377315</v>
       </c>
       <c r="G62" t="n">
-        <v>-1.80428779329544</v>
+        <v>-1.80431179305565</v>
       </c>
       <c r="H62" t="n">
-        <v>0.0711862023827968</v>
+        <v>0.0711824420644727</v>
       </c>
       <c r="I62" t="n">
-        <v>-0.105213020683997</v>
+        <v>-0.105213397792272</v>
       </c>
       <c r="J62" t="n">
-        <v>0.00435123984688499</v>
+        <v>0.00435055689526229</v>
       </c>
     </row>
     <row r="63">
@@ -2500,22 +2500,22 @@
         <v>13</v>
       </c>
       <c r="E63" t="n">
-        <v>0.216338440163474</v>
+        <v>0.216338609007019</v>
       </c>
       <c r="F63" t="n">
-        <v>0.0396573187543716</v>
+        <v>0.0396575688443174</v>
       </c>
       <c r="G63" t="n">
-        <v>5.45519583669853</v>
+        <v>5.45516569248844</v>
       </c>
       <c r="H63" t="n">
-        <v>0.0000000489189010872183</v>
+        <v>0.0000000489272007383966</v>
       </c>
       <c r="I63" t="n">
-        <v>0.138611523681481</v>
+        <v>0.138611202357739</v>
       </c>
       <c r="J63" t="n">
-        <v>0.294065356645467</v>
+        <v>0.294066015656299</v>
       </c>
     </row>
     <row r="64">
@@ -2532,22 +2532,22 @@
         <v>13</v>
       </c>
       <c r="E64" t="n">
-        <v>0.0906360744475766</v>
+        <v>0.0845292407738183</v>
       </c>
       <c r="F64" t="n">
-        <v>0.0364756065724049</v>
+        <v>0.0367301314091718</v>
       </c>
       <c r="G64" t="n">
-        <v>2.48484077345395</v>
+        <v>2.30135960669911</v>
       </c>
       <c r="H64" t="n">
-        <v>0.0129609391969533</v>
+        <v>0.0213713131168247</v>
       </c>
       <c r="I64" t="n">
-        <v>0.0191451992514105</v>
+        <v>0.0125395060644181</v>
       </c>
       <c r="J64" t="n">
-        <v>0.162126949643743</v>
+        <v>0.156518975483218</v>
       </c>
     </row>
     <row r="65">
@@ -2564,22 +2564,22 @@
         <v>13</v>
       </c>
       <c r="E65" t="n">
-        <v>-0.0179458476728954</v>
+        <v>-0.0195714816454934</v>
       </c>
       <c r="F65" t="n">
-        <v>0.0299485778445299</v>
+        <v>0.0299700663843328</v>
       </c>
       <c r="G65" t="n">
-        <v>-0.599222032046279</v>
+        <v>-0.653034310785665</v>
       </c>
       <c r="H65" t="n">
-        <v>0.549024832598885</v>
+        <v>0.513734159169028</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.0766439816363681</v>
+        <v>-0.0783117323730603</v>
       </c>
       <c r="J65" t="n">
-        <v>0.0407522862905774</v>
+        <v>0.0391687690820734</v>
       </c>
     </row>
     <row r="66">
@@ -2596,22 +2596,22 @@
         <v>13</v>
       </c>
       <c r="E66" t="n">
-        <v>0.0321330936069027</v>
+        <v>0.0321330933915048</v>
       </c>
       <c r="F66" t="n">
-        <v>0.0105497553714068</v>
+        <v>0.0105497545061429</v>
       </c>
       <c r="G66" t="n">
-        <v>3.04586148926197</v>
+        <v>3.04586171865843</v>
       </c>
       <c r="H66" t="n">
-        <v>0.00232014690890964</v>
+        <v>0.00232014513883104</v>
       </c>
       <c r="I66" t="n">
-        <v>0.0114559530332373</v>
+        <v>0.0114559545137256</v>
       </c>
       <c r="J66" t="n">
-        <v>0.052810234180568</v>
+        <v>0.052810232269284</v>
       </c>
     </row>
     <row r="67">
@@ -2628,22 +2628,22 @@
         <v>13</v>
       </c>
       <c r="E67" t="n">
-        <v>0.0638952078958447</v>
+        <v>0.0644683593527544</v>
       </c>
       <c r="F67" t="n">
-        <v>0.0103486179241968</v>
+        <v>0.0104192018166239</v>
       </c>
       <c r="G67" t="n">
-        <v>6.17427451316441</v>
+        <v>6.18745662934514</v>
       </c>
       <c r="H67" t="n">
-        <v>0.00000000066467967478612</v>
+        <v>0.000000000611426612973281</v>
       </c>
       <c r="I67" t="n">
-        <v>0.0436122894746533</v>
+        <v>0.0440470990445172</v>
       </c>
       <c r="J67" t="n">
-        <v>0.0841781263170361</v>
+        <v>0.0848896196609915</v>
       </c>
     </row>
     <row r="68">
@@ -2660,22 +2660,22 @@
         <v>13</v>
       </c>
       <c r="E68" t="n">
-        <v>0.0210201862572694</v>
+        <v>0.0227497052505084</v>
       </c>
       <c r="F68" t="n">
-        <v>0.0222887589823777</v>
+        <v>0.0225083614548417</v>
       </c>
       <c r="G68" t="n">
-        <v>0.943084640732519</v>
+        <v>1.0107224062556</v>
       </c>
       <c r="H68" t="n">
-        <v>0.345637611269397</v>
+        <v>0.312149309883695</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.0226649786082845</v>
+        <v>-0.021365872551991</v>
       </c>
       <c r="J68" t="n">
-        <v>0.0647053511228234</v>
+        <v>0.0668652830530077</v>
       </c>
     </row>
     <row r="69">
@@ -2692,22 +2692,22 @@
         <v>13</v>
       </c>
       <c r="E69" t="n">
-        <v>0.025863827609735</v>
+        <v>0.0262732992092484</v>
       </c>
       <c r="F69" t="n">
-        <v>0.0207510097018319</v>
+        <v>0.0208352077427584</v>
       </c>
       <c r="G69" t="n">
-        <v>1.24638887366776</v>
+        <v>1.26100490734872</v>
       </c>
       <c r="H69" t="n">
-        <v>0.21262166401872</v>
+        <v>0.207307079095575</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.0148074040486967</v>
+        <v>-0.0145629575769681</v>
       </c>
       <c r="J69" t="n">
-        <v>0.0665350592681667</v>
+        <v>0.067109555995465</v>
       </c>
     </row>
     <row r="70">
@@ -2724,22 +2724,22 @@
         <v>13</v>
       </c>
       <c r="E70" t="n">
-        <v>0.00603234707827679</v>
+        <v>0.00603236867842486</v>
       </c>
       <c r="F70" t="n">
-        <v>0.00739249007764963</v>
+        <v>0.00739249154081246</v>
       </c>
       <c r="G70" t="n">
-        <v>0.816010169092404</v>
+        <v>0.816012929486814</v>
       </c>
       <c r="H70" t="n">
-        <v>0.414494319615637</v>
+        <v>0.414492740847638</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.00845666722998619</v>
+        <v>-0.00845664849758456</v>
       </c>
       <c r="J70" t="n">
-        <v>0.0205213613865398</v>
+        <v>0.0205213858544343</v>
       </c>
     </row>
     <row r="71">
@@ -2756,22 +2756,22 @@
         <v>13</v>
       </c>
       <c r="E71" t="n">
-        <v>-0.00394012583695153</v>
+        <v>-0.00437812207286894</v>
       </c>
       <c r="F71" t="n">
-        <v>0.00317981363950169</v>
+        <v>0.00323232814497959</v>
       </c>
       <c r="G71" t="n">
-        <v>-1.23910589853593</v>
+        <v>-1.35447945768408</v>
       </c>
       <c r="H71" t="n">
-        <v>0.215306282884372</v>
+        <v>0.175583462798492</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.0101724460479241</v>
+        <v>-0.0107133688232441</v>
       </c>
       <c r="J71" t="n">
-        <v>0.00229219437402101</v>
+        <v>0.00195712467750622</v>
       </c>
     </row>
     <row r="72">
@@ -2788,22 +2788,22 @@
         <v>13</v>
       </c>
       <c r="E72" t="n">
-        <v>0.00251690335827439</v>
+        <v>0.00251169837886602</v>
       </c>
       <c r="F72" t="n">
-        <v>0.00766994937312625</v>
+        <v>0.00768547154386933</v>
       </c>
       <c r="G72" t="n">
-        <v>0.328151234882076</v>
+        <v>0.326811226159518</v>
       </c>
       <c r="H72" t="n">
-        <v>0.742797316961904</v>
+        <v>0.743810668027666</v>
       </c>
       <c r="I72" t="n">
-        <v>-0.0125159211762986</v>
+        <v>-0.0125515490513253</v>
       </c>
       <c r="J72" t="n">
-        <v>0.0175497278928474</v>
+        <v>0.0175749458090573</v>
       </c>
     </row>
     <row r="73">
@@ -2820,22 +2820,22 @@
         <v>13</v>
       </c>
       <c r="E73" t="n">
-        <v>0.317258852025139</v>
+        <v>0.258394996530574</v>
       </c>
       <c r="F73" t="n">
-        <v>0.0539286322468769</v>
+        <v>0.0559411425643011</v>
       </c>
       <c r="G73" t="n">
-        <v>5.88293896594257</v>
+        <v>4.61905110775247</v>
       </c>
       <c r="H73" t="n">
-        <v>0.00000000403044585300837</v>
+        <v>0.00000385498905404878</v>
       </c>
       <c r="I73" t="n">
-        <v>0.211560675085755</v>
+        <v>0.148752371850523</v>
       </c>
       <c r="J73" t="n">
-        <v>0.422957028964523</v>
+        <v>0.368037621210624</v>
       </c>
     </row>
     <row r="74">
@@ -2852,22 +2852,22 @@
         <v>13</v>
       </c>
       <c r="E74" t="n">
-        <v>0.0419674056057879</v>
+        <v>0.015476769166854</v>
       </c>
       <c r="F74" t="n">
-        <v>0.0576538641301704</v>
+        <v>0.0570371400379573</v>
       </c>
       <c r="G74" t="n">
-        <v>0.727920083743811</v>
+        <v>0.271345462913367</v>
       </c>
       <c r="H74" t="n">
-        <v>0.46666250818645</v>
+        <v>0.786125343216235</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.0710320916589117</v>
+        <v>-0.0963139710887097</v>
       </c>
       <c r="J74" t="n">
-        <v>0.154966902870487</v>
+        <v>0.127267509422418</v>
       </c>
     </row>
     <row r="75">
@@ -2884,22 +2884,22 @@
         <v>13</v>
       </c>
       <c r="E75" t="n">
-        <v>0.82395155310406</v>
+        <v>0.796286804215643</v>
       </c>
       <c r="F75" t="n">
-        <v>0.0252287900001602</v>
+        <v>0.0245428148583701</v>
       </c>
       <c r="G75" t="n">
-        <v>32.6591783870264</v>
+        <v>32.4448034510629</v>
       </c>
       <c r="H75" t="n">
-        <v>5.93633932126461e-234</v>
+        <v>6.41245136327593e-231</v>
       </c>
       <c r="I75" t="n">
-        <v>0.774504033330222</v>
+        <v>0.748183771014004</v>
       </c>
       <c r="J75" t="n">
-        <v>0.873399072877898</v>
+        <v>0.844389837417283</v>
       </c>
     </row>
     <row r="76">
@@ -2916,22 +2916,22 @@
         <v>51</v>
       </c>
       <c r="E76" t="n">
-        <v>0.358009115654118</v>
+        <v>0.322625551546674</v>
       </c>
       <c r="F76" t="n">
-        <v>0.0494347404130465</v>
+        <v>0.0441498170213269</v>
       </c>
       <c r="G76" t="n">
-        <v>7.24205513496808</v>
+        <v>7.3075172970893</v>
       </c>
       <c r="H76" t="n">
-        <v>0.000000000000441936106708543</v>
+        <v>0.000000000000272123305261024</v>
       </c>
       <c r="I76" t="n">
-        <v>0.26111880485946</v>
+        <v>0.23609350026084</v>
       </c>
       <c r="J76" t="n">
-        <v>0.454899426448775</v>
+        <v>0.409157602832508</v>
       </c>
     </row>
     <row r="77">
@@ -2948,22 +2948,22 @@
         <v>13</v>
       </c>
       <c r="E77" t="n">
-        <v>-0.513022774412146</v>
+        <v>-0.429773653009528</v>
       </c>
       <c r="F77" t="n">
-        <v>0.0623503319839432</v>
+        <v>0.0590287938626119</v>
       </c>
       <c r="G77" t="n">
-        <v>-8.2280680485272</v>
+        <v>-7.2807459696672</v>
       </c>
       <c r="H77" t="n">
-        <v>0.000000000000000190256995991034</v>
+        <v>0.000000000000331979293573258</v>
       </c>
       <c r="I77" t="n">
-        <v>-0.635227179524791</v>
+        <v>-0.545467963031086</v>
       </c>
       <c r="J77" t="n">
-        <v>-0.390818369299502</v>
+        <v>-0.314079342987969</v>
       </c>
     </row>
     <row r="78">
@@ -2980,22 +2980,22 @@
         <v>13</v>
       </c>
       <c r="E78" t="n">
-        <v>0.587856774480822</v>
+        <v>0.575598614312547</v>
       </c>
       <c r="F78" t="n">
-        <v>0.0304765306439197</v>
+        <v>0.0300392012925491</v>
       </c>
       <c r="G78" t="n">
-        <v>19.2888351154269</v>
+        <v>19.1615818512231</v>
       </c>
       <c r="H78" t="n">
-        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000666583317991918</v>
+        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000774822791451221</v>
       </c>
       <c r="I78" t="n">
-        <v>0.528123872045008</v>
+        <v>0.516722861654801</v>
       </c>
       <c r="J78" t="n">
-        <v>0.647589676916636</v>
+        <v>0.634474366970292</v>
       </c>
     </row>
     <row r="79">
@@ -3012,22 +3012,22 @@
         <v>13</v>
       </c>
       <c r="E79" t="n">
-        <v>0.44152696905055</v>
+        <v>0.435403936121988</v>
       </c>
       <c r="F79" t="n">
-        <v>0.0517251849324346</v>
+        <v>0.0502858186011699</v>
       </c>
       <c r="G79" t="n">
-        <v>8.53601528205823</v>
+        <v>8.65858304058431</v>
       </c>
       <c r="H79" t="n">
-        <v>0.0000000000000000138929995034669</v>
+        <v>0.00000000000000000477664601605288</v>
       </c>
       <c r="I79" t="n">
-        <v>0.340147469489304</v>
+        <v>0.336845542730581</v>
       </c>
       <c r="J79" t="n">
-        <v>0.542906468611795</v>
+        <v>0.533962329513396</v>
       </c>
     </row>
     <row r="80">
@@ -3044,22 +3044,22 @@
         <v>52</v>
       </c>
       <c r="E80" t="n">
-        <v>-0.322133303360374</v>
+        <v>-0.299153517934629</v>
       </c>
       <c r="F80" t="n">
-        <v>0.0520739503781553</v>
+        <v>0.0549751182730622</v>
       </c>
       <c r="G80" t="n">
-        <v>-6.18607386267179</v>
+        <v>-5.44161663188661</v>
       </c>
       <c r="H80" t="n">
-        <v>0.000000000616811151857916</v>
+        <v>0.0000000527992066444612</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.424196370634284</v>
+        <v>-0.406902769795661</v>
       </c>
       <c r="J80" t="n">
-        <v>-0.220070236086464</v>
+        <v>-0.191404266073597</v>
       </c>
     </row>
     <row r="81">
@@ -3076,22 +3076,22 @@
         <v>13</v>
       </c>
       <c r="E81" t="n">
-        <v>0.0636659406872371</v>
+        <v>0.0614673130834829</v>
       </c>
       <c r="F81" t="n">
-        <v>0.00907809124498518</v>
+        <v>0.00909673177382162</v>
       </c>
       <c r="G81" t="n">
-        <v>7.01314174633425</v>
+        <v>6.75707656461546</v>
       </c>
       <c r="H81" t="n">
-        <v>0.0000000000023302515106238</v>
+        <v>0.0000000000140803793972731</v>
       </c>
       <c r="I81" t="n">
-        <v>0.0458732087986977</v>
+        <v>0.0436380464297714</v>
       </c>
       <c r="J81" t="n">
-        <v>0.0814586725757764</v>
+        <v>0.0792965797371945</v>
       </c>
     </row>
     <row r="82">
@@ -3108,22 +3108,22 @@
         <v>53</v>
       </c>
       <c r="E82" t="n">
-        <v>0.539732200138629</v>
+        <v>0.540939664837664</v>
       </c>
       <c r="F82" t="n">
-        <v>0.0257040960276336</v>
+        <v>0.0257788851946591</v>
       </c>
       <c r="G82" t="n">
-        <v>20.9979063087214</v>
+        <v>20.983826909231</v>
       </c>
       <c r="H82" t="n">
-        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000685401796824756</v>
+        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000921692594554504</v>
       </c>
       <c r="I82" t="n">
-        <v>0.489353097669308</v>
+        <v>0.49041397829454</v>
       </c>
       <c r="J82" t="n">
-        <v>0.59011130260795</v>
+        <v>0.591465351380789</v>
       </c>
     </row>
     <row r="83">
@@ -3140,22 +3140,22 @@
         <v>13</v>
       </c>
       <c r="E83" t="n">
-        <v>0.107534618944656</v>
+        <v>0.107855336791101</v>
       </c>
       <c r="F83" t="n">
-        <v>0.011052547459949</v>
+        <v>0.0112309273370164</v>
       </c>
       <c r="G83" t="n">
-        <v>9.72939671458806</v>
+        <v>9.60342218897786</v>
       </c>
       <c r="H83" t="n">
-        <v>0.000000000000000000000225928874643716</v>
+        <v>0.000000000000000000000773332305169332</v>
       </c>
       <c r="I83" t="n">
-        <v>0.0858720239857366</v>
+        <v>0.0858431236975629</v>
       </c>
       <c r="J83" t="n">
-        <v>0.129197213903576</v>
+        <v>0.12986754988464</v>
       </c>
     </row>
   </sheetData>
